--- a/Sep_2026/Daily Sale/25-09-26/Zeshan.xlsx
+++ b/Sep_2026/Daily Sale/25-09-26/Zeshan.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AFA1C4-A428-45AF-8846-82364CC7F393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B9A92C-58B7-4200-AEE1-B1FAEA7BCA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="523">
   <si>
     <t>Sr.No</t>
   </si>
@@ -1614,13 +1614,16 @@
     <t>Fakhir Store</t>
   </si>
   <si>
-    <t>Yaseen Store</t>
-  </si>
-  <si>
     <t>Bilal Store</t>
   </si>
   <si>
     <t>Moon Store</t>
+  </si>
+  <si>
+    <t>D Mart</t>
+  </si>
+  <si>
+    <t>Address: Banker Society</t>
   </si>
 </sst>
 </file>
@@ -7209,7 +7212,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="400" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B6" s="400"/>
       <c r="C6" s="400"/>
@@ -8635,7 +8638,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="400" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B6" s="400"/>
       <c r="C6" s="400"/>
@@ -47958,7 +47961,7 @@
       <c r="L4" s="395"/>
       <c r="M4" s="398">
         <f ca="1">TODAY()+1</f>
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="N4" s="398"/>
       <c r="O4" s="398"/>
@@ -47986,7 +47989,7 @@
       <c r="L5" s="395"/>
       <c r="M5" s="398">
         <f ca="1">M4-1</f>
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="N5" s="394"/>
       <c r="O5" s="394"/>
@@ -54421,7 +54424,7 @@
       </c>
       <c r="S7" s="300" t="str">
         <f>+'5'!A6:A6</f>
-        <v>Yaseen Store</v>
+        <v>D Mart</v>
       </c>
       <c r="T7" s="301">
         <f>+'5'!P35</f>
@@ -61441,7 +61444,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="400" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B6" s="400"/>
       <c r="C6" s="400"/>
@@ -61498,7 +61501,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="401" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B8" s="401"/>
       <c r="C8" s="401"/>
@@ -62722,7 +62725,7 @@
     <mergeCell ref="K4:M4"/>
     <mergeCell ref="N4:P4"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0800-000000000000}">
       <formula1>$XFC$3:$XFC$4</formula1>
     </dataValidation>
@@ -62737,7 +62740,7 @@
   <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0800-000003000000}">
           <x14:formula1>
             <xm:f>Summary!$B$44:$B$51</xm:f>
